--- a/results/config/overall_summary_no_repulsion.xlsx
+++ b/results/config/overall_summary_no_repulsion.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,6 +607,83 @@
         <v>30</v>
       </c>
       <c r="W2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>kjsd__advperagentrankweighted__M4__L24__eps0p01__g0p0005__ds1__dm1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>jsd</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>peragentrankweighted</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>31</v>
+      </c>
+      <c r="L3" t="n">
+        <v>7.358955472479114</v>
+      </c>
+      <c r="M3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N3" t="n">
+        <v>7</v>
+      </c>
+      <c r="O3" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.9277722553567487</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.1624068949371576</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.1504096228008469</v>
+      </c>
+      <c r="V3" t="n">
+        <v>30</v>
+      </c>
+      <c r="W3" t="n">
         <v>30</v>
       </c>
     </row>
